--- a/Documentation/Excel/fonction_octopus_diagram.xlsx
+++ b/Documentation/Excel/fonction_octopus_diagram.xlsx
@@ -5,22 +5,22 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexv\Documents\Etude\POLYTECH\4AGPSE\Projet\depot_git\gyrobot_file\gyrobot\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nomis\Documents\Polytech\GPSE\4A\Projet\gyrobot\Documentation\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AF88110A-5065-480E-AF17-0CD3DA2FC864}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C9C0CEA-1B8A-4644-8DEB-0CF32D912F0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{47ABDAC5-2A6E-4879-ACA9-2CAB6E1A448D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{47ABDAC5-2A6E-4879-ACA9-2CAB6E1A448D}"/>
   </bookViews>
   <sheets>
     <sheet name="fct" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="55">
   <si>
     <t>Service function</t>
   </si>
@@ -112,9 +112,6 @@
     <t>± 2m</t>
   </si>
   <si>
-    <t>Lidar (.LAS) range</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 5 cm</t>
   </si>
   <si>
@@ -182,6 +179,12 @@
   </si>
   <si>
     <t>&lt; 50 ms</t>
+  </si>
+  <si>
+    <t>LiDAR max range</t>
+  </si>
+  <si>
+    <t>-3cm + 5cm</t>
   </si>
 </sst>
 </file>
@@ -712,7 +715,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -723,10 +726,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
@@ -735,8 +741,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1114,15 +1120,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9573505-A2EB-4841-97DF-8F2A2030B85A}">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="83.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="11.5546875" style="1"/>
+    <col min="1" max="1" width="83.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="11.54296875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1136,246 +1142,246 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="6"/>
+      <c r="B3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="6"/>
+      <c r="B5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="6"/>
+      <c r="B6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="6"/>
+      <c r="B7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="6"/>
+      <c r="B9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="6"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="6"/>
+      <c r="B12" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" s="6"/>
+      <c r="B15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="3"/>
-      <c r="B3" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="3"/>
-      <c r="B5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="3"/>
-      <c r="B6" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="3"/>
-      <c r="B7" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="4" t="s">
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="6"/>
+      <c r="B17" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="3"/>
-      <c r="B9" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="3"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="3"/>
-      <c r="B12" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="3"/>
-      <c r="B15" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="3"/>
-      <c r="B17" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" s="5">
-        <v>0.8</v>
-      </c>
-      <c r="D17" s="4" t="s">
+    </row>
+    <row r="19" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A19" s="6"/>
+      <c r="B19" s="5" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C18" s="4" t="s">
+      <c r="C19" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D18" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="3"/>
-      <c r="B19" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C19" s="4" t="s">
+      <c r="D19" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="6"/>
+      <c r="B20" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D19" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="3"/>
-      <c r="B20" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D20" s="4" t="s">
-        <v>37</v>
+      <c r="D20" s="3" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/Documentation/Excel/fonction_octopus_diagram.xlsx
+++ b/Documentation/Excel/fonction_octopus_diagram.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nomis\Documents\Polytech\GPSE\4A\Projet\gyrobot\Documentation\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\haasm\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C9C0CEA-1B8A-4644-8DEB-0CF32D912F0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED282D65-EF1C-47B1-B8C5-9DB9C305B85C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{47ABDAC5-2A6E-4879-ACA9-2CAB6E1A448D}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="21060" windowHeight="15585" xr2:uid="{47ABDAC5-2A6E-4879-ACA9-2CAB6E1A448D}"/>
   </bookViews>
   <sheets>
     <sheet name="fct" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="65">
   <si>
     <t>Service function</t>
   </si>
@@ -185,13 +185,43 @@
   </si>
   <si>
     <t>-3cm + 5cm</t>
+  </si>
+  <si>
+    <t>Battery replacement (FP5) : Allow the user to replace and handle the battery</t>
+  </si>
+  <si>
+    <t>Replacement time</t>
+  </si>
+  <si>
+    <t>&lt; 1 min</t>
+  </si>
+  <si>
+    <t>Tools required for access</t>
+  </si>
+  <si>
+    <t>Connector safety</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>Accessibility and safety (FC2) : Facilitate access and ensure safe handling</t>
+  </si>
+  <si>
+    <t>Power supply (FC3) : Supply electrical power</t>
+  </si>
+  <si>
+    <t>Minimum autonomy</t>
+  </si>
+  <si>
+    <t>Nominal voltage</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -325,6 +355,11 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="34">
@@ -715,7 +750,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -732,6 +767,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -741,7 +782,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1119,16 +1163,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9573505-A2EB-4841-97DF-8F2A2030B85A}">
-  <dimension ref="A1:D20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:D25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="83.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="11.54296875" style="1"/>
+    <col min="1" max="1" width="83.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="11.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1142,8 +1186,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:4">
+      <c r="A2" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -1152,12 +1196,12 @@
       <c r="C2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="7" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="6"/>
+    <row r="3" spans="1:4">
+      <c r="A3" s="8"/>
       <c r="B3" s="3" t="s">
         <v>53</v>
       </c>
@@ -1168,8 +1212,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="6" t="s">
+    <row r="4" spans="1:4">
+      <c r="A4" s="8" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -1182,8 +1226,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="6"/>
+    <row r="5" spans="1:4">
+      <c r="A5" s="8"/>
       <c r="B5" s="3" t="s">
         <v>8</v>
       </c>
@@ -1194,8 +1238,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="6"/>
+    <row r="6" spans="1:4">
+      <c r="A6" s="8"/>
       <c r="B6" s="3" t="s">
         <v>25</v>
       </c>
@@ -1206,8 +1250,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="6"/>
+    <row r="7" spans="1:4">
+      <c r="A7" s="8"/>
       <c r="B7" s="3" t="s">
         <v>32</v>
       </c>
@@ -1218,8 +1262,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="6" t="s">
+    <row r="8" spans="1:4">
+      <c r="A8" s="8" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -1232,8 +1276,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="6"/>
+    <row r="9" spans="1:4">
+      <c r="A9" s="8"/>
       <c r="B9" s="3" t="s">
         <v>11</v>
       </c>
@@ -1244,11 +1288,11 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="6" t="s">
+    <row r="10" spans="1:4">
+      <c r="A10" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="9" t="s">
         <v>13</v>
       </c>
       <c r="C10" s="3" t="s">
@@ -1258,9 +1302,9 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="6"/>
-      <c r="B11" s="8"/>
+    <row r="11" spans="1:4">
+      <c r="A11" s="8"/>
+      <c r="B11" s="10"/>
       <c r="C11" s="3" t="s">
         <v>50</v>
       </c>
@@ -1268,8 +1312,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="6"/>
+    <row r="12" spans="1:4">
+      <c r="A12" s="8"/>
       <c r="B12" s="3" t="s">
         <v>14</v>
       </c>
@@ -1280,120 +1324,188 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:4">
+      <c r="A13" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="6" t="s">
+      <c r="D14" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="10"/>
+      <c r="B16" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="10"/>
+      <c r="B18" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B19" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C19" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="6"/>
-      <c r="B15" s="3" t="s">
+      <c r="D19" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="8"/>
+      <c r="B20" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C20" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="6" t="s">
+      <c r="D20" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B21" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C21" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="6"/>
-      <c r="B17" s="3" t="s">
+    <row r="22" spans="1:4">
+      <c r="A22" s="8"/>
+      <c r="B22" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C22" s="4">
         <v>0.8</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D22" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="6" t="s">
+    <row r="23" spans="1:4">
+      <c r="A23" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B23" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C23" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A19" s="6"/>
-      <c r="B19" s="5" t="s">
+      <c r="D23" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="30">
+      <c r="A24" s="8"/>
+      <c r="B24" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C24" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="6"/>
-      <c r="B20" s="3" t="s">
+      <c r="D24" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="8"/>
+      <c r="B25" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C25" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D25" s="3" t="s">
         <v>36</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A16:A17"/>
+  <mergeCells count="10">
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A21:A22"/>
     <mergeCell ref="B10:B11"/>
-    <mergeCell ref="A18:A20"/>
+    <mergeCell ref="A23:A25"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A19:A20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Documentation/Excel/fonction_octopus_diagram.xlsx
+++ b/Documentation/Excel/fonction_octopus_diagram.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nomis\Documents\Polytech\GPSE\4A\Projet\gyrobot\Documentation\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C9C0CEA-1B8A-4644-8DEB-0CF32D912F0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FF4F2A1-F13C-4C3A-97B1-76009AF4BF83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{47ABDAC5-2A6E-4879-ACA9-2CAB6E1A448D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{47ABDAC5-2A6E-4879-ACA9-2CAB6E1A448D}"/>
   </bookViews>
   <sheets>
     <sheet name="fct" sheetId="1" r:id="rId1"/>
@@ -118,9 +118,6 @@
     <t>± 5cm</t>
   </si>
   <si>
-    <t>Minimum turning radius (at 4 km/h)</t>
-  </si>
-  <si>
     <t>± 2 km/h</t>
   </si>
   <si>
@@ -185,6 +182,9 @@
   </si>
   <si>
     <t>-3cm + 5cm</t>
+  </si>
+  <si>
+    <t>Turning radius (at 4 km/h)</t>
   </si>
 </sst>
 </file>
@@ -732,6 +732,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -739,9 +742,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1120,15 +1120,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9573505-A2EB-4841-97DF-8F2A2030B85A}">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="83.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="11.54296875" style="1"/>
+    <col min="1" max="1" width="91.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="11.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1142,8 +1142,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -1152,14 +1152,14 @@
       <c r="C2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="9" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="6"/>
+      <c r="D2" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="7"/>
       <c r="B3" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>28</v>
@@ -1168,8 +1168,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="6" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -1179,11 +1179,11 @@
         <v>7</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="6"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="7"/>
       <c r="B5" s="3" t="s">
         <v>8</v>
       </c>
@@ -1191,11 +1191,11 @@
         <v>7</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="6"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="7"/>
       <c r="B6" s="3" t="s">
         <v>25</v>
       </c>
@@ -1203,84 +1203,84 @@
         <v>26</v>
       </c>
       <c r="D6" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="7"/>
+      <c r="B7" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="6"/>
-      <c r="B7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="6" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="6"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="7"/>
       <c r="B9" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="8" t="s">
         <v>13</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="7"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="6"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="D11" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="6"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="7"/>
       <c r="B12" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>15</v>
       </c>
@@ -1288,54 +1288,54 @@
         <v>16</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
         <v>17</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="6"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="7"/>
       <c r="B15" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
         <v>20</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="6"/>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="7"/>
       <c r="B17" s="3" t="s">
         <v>22</v>
       </c>
@@ -1343,45 +1343,45 @@
         <v>0.8</v>
       </c>
       <c r="D17" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="7"/>
+      <c r="B19" s="5" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C18" s="3" t="s">
+      <c r="C19" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A19" s="6"/>
-      <c r="B19" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="7"/>
+      <c r="B20" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="6"/>
-      <c r="B20" s="3" t="s">
-        <v>46</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
